--- a/data/trans_orig/P57B2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido feliz en 2023</t>
+          <t>Población según se ha sentido feliz en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78886</t>
+          <t>78220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>95860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201225</t>
+          <t>203369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246657</t>
+          <t>246864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225143</t>
+          <t>225459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245580</t>
+          <t>245693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429260</t>
+          <t>432526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483694</t>
+          <t>484813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>46048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63069</t>
+          <t>62057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90824</t>
+          <t>91137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2959</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307261</t>
+          <t>307939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361770</t>
+          <t>362336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>268991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>307313</t>
+          <t>307483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>592456</t>
+          <t>594883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>661621</t>
+          <t>661420</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124848</t>
+          <t>123795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176583</t>
+          <t>175807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168073</t>
+          <t>167643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206501</t>
+          <t>206092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300603</t>
+          <t>302890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367382</t>
+          <t>368013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43874</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>75843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181780</t>
+          <t>183193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>215462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183978</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213267</t>
+          <t>215510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>374351</t>
+          <t>376720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>420354</t>
+          <t>420644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50335</t>
+          <t>49988</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76014</t>
+          <t>75828</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73109</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99979</t>
+          <t>98888</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>129149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>167475</t>
+          <t>165552</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>57217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>59637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79208</t>
+          <t>78733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108809</t>
+          <t>109499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173803</t>
+          <t>171993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211810</t>
+          <t>211332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>132816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259710</t>
+          <t>259597</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>296450</t>
+          <t>290941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>461051</t>
+          <t>457651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>64765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97966</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147684</t>
+          <t>149304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309868</t>
+          <t>309211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224363</t>
+          <t>226617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434583</t>
+          <t>424451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57717</t>
+          <t>57533</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47849</t>
+          <t>45478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84918</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46569</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>46321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71419</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78420</t>
+          <t>78535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101866</t>
+          <t>101803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>92305</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113696</t>
+          <t>112617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178396</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>207772</t>
+          <t>208951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60514</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70450</t>
+          <t>71033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>89707</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116843</t>
+          <t>116994</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144599</t>
+          <t>144517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>141656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>172638</t>
+          <t>169833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131926</t>
+          <t>131321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156940</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>281819</t>
+          <t>281812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>318603</t>
+          <t>320538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80790</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67723</t>
+          <t>69629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>105884</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140903</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>63972</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>273683</t>
+          <t>271795</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>333532</t>
+          <t>331595</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>346358</t>
+          <t>342633</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>661723</t>
+          <t>666318</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>650129</t>
+          <t>644961</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1035365</t>
+          <t>1008050</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>208044</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>265710</t>
+          <t>268581</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>135445</t>
+          <t>136411</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>377839</t>
+          <t>379866</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>325869</t>
+          <t>339716</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>616249</t>
+          <t>618868</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84546</t>
+          <t>85739</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38341</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>109615</t>
+          <t>111487</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>89252</t>
+          <t>93194</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>179658</t>
+          <t>180626</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>34168</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>407443</t>
+          <t>402292</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>763643</t>
+          <t>766995</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>243239</t>
+          <t>245967</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>293405</t>
+          <t>290679</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>665098</t>
+          <t>662534</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1126318</t>
+          <t>1146081</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>108769</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>343649</t>
+          <t>348149</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>242641</t>
+          <t>245169</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>285963</t>
+          <t>287714</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>314346</t>
+          <t>312228</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>616113</t>
+          <t>610709</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>155633</t>
+          <t>157719</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>145714</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>186480</t>
+          <t>183340</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>166726</t>
+          <t>159626</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>326677</t>
+          <t>331675</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1680746</t>
+          <t>1679159</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2203223</t>
+          <t>2173471</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1465798</t>
+          <t>1467580</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2018492</t>
+          <t>2037453</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3188875</t>
+          <t>3194979</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3900777</t>
+          <t>3926612</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>877855</t>
+          <t>907561</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1267016</t>
+          <t>1271478</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1161807</t>
+          <t>1160249</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1552222</t>
+          <t>1560092</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2269600</t>
+          <t>2268320</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2790536</t>
+          <t>2792173</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>432440</t>
+          <t>430218</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>433337</t>
+          <t>429833</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>581781</t>
+          <t>585367</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>790006</t>
+          <t>794288</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>992459</t>
+          <t>993940</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>55565</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>95683</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>93158</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>126868</t>
+          <t>126612</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>177960</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>28800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78220</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61972</t>
+          <t>52428</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95860</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>227059</t>
+          <t>243035</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203369</t>
+          <t>226365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246864</t>
+          <t>258963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>235977</t>
+          <t>253719</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225459</t>
+          <t>240751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245693</t>
+          <t>264952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>463034</t>
+          <t>496754</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>432526</t>
+          <t>474719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484813</t>
+          <t>516801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>35070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46048</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>40798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>61653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>85172</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62057</t>
+          <t>70876</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91137</t>
+          <t>99906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>551</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>551</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>336782</t>
+          <t>343767</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307939</t>
+          <t>313102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>362336</t>
+          <t>369674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>290070</t>
+          <t>307410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>268991</t>
+          <t>287511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>307483</t>
+          <t>326717</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>626852</t>
+          <t>651177</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>594883</t>
+          <t>610690</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>661420</t>
+          <t>683779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>149642</t>
+          <t>153847</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123795</t>
+          <t>129477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175807</t>
+          <t>181736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>185176</t>
+          <t>198749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167643</t>
+          <t>179474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206092</t>
+          <t>219410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>334818</t>
+          <t>352596</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>302890</t>
+          <t>321575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>368013</t>
+          <t>389771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>57777</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45214</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75843</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>543895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>543895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>543895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1030847</t>
+          <t>1074542</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1030847</t>
+          <t>1074542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1030847</t>
+          <t>1074542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>199369</t>
+          <t>194902</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183193</t>
+          <t>177510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215462</t>
+          <t>210091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>199334</t>
+          <t>200969</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>186209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215510</t>
+          <t>216003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>398703</t>
+          <t>395871</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376720</t>
+          <t>374205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>420644</t>
+          <t>416825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62033</t>
+          <t>64460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49988</t>
+          <t>52178</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75828</t>
+          <t>79037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85562</t>
+          <t>88581</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72581</t>
+          <t>74359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98888</t>
+          <t>103350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>153041</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>129149</t>
+          <t>135533</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>165552</t>
+          <t>173038</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57217</t>
+          <t>57713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39043</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>93199</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78733</t>
+          <t>82393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109499</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>24203</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31451</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>346796</t>
+          <t>354002</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346796</t>
+          <t>354002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346796</t>
+          <t>354002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>662847</t>
+          <t>669995</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>662847</t>
+          <t>669995</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>662847</t>
+          <t>669995</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>193737</t>
+          <t>235726</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>171993</t>
+          <t>212462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211332</t>
+          <t>257881</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>205469</t>
+          <t>235281</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132816</t>
+          <t>216005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259597</t>
+          <t>254619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>471006</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290941</t>
+          <t>439309</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457651</t>
+          <t>500637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>75374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>116452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>214899</t>
+          <t>126002</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149304</t>
+          <t>109938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309211</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>294527</t>
+          <t>220835</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226617</t>
+          <t>194718</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>424451</t>
+          <t>250117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>37381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>61385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>57434</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85618</t>
+          <t>89640</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>300467</t>
+          <t>359656</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>300467</t>
+          <t>359656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>300467</t>
+          <t>359656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>471478</t>
+          <t>417418</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471478</t>
+          <t>417418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>471478</t>
+          <t>417418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>771945</t>
+          <t>777074</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>771945</t>
+          <t>777074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>771945</t>
+          <t>777074</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35612</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25925</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47867</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>55694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71689</t>
+          <t>85835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>90672</t>
+          <t>101373</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>88163</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101803</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>102854</t>
+          <t>111925</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92305</t>
+          <t>100927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112617</t>
+          <t>124013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>193526</t>
+          <t>213299</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178144</t>
+          <t>198104</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208951</t>
+          <t>231639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61691</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>74671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89707</t>
+          <t>95912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>130769</t>
+          <t>145149</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116994</t>
+          <t>130958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144517</t>
+          <t>160475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178125</t>
+          <t>205063</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178125</t>
+          <t>205063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178125</t>
+          <t>205063</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>386399</t>
+          <t>431887</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>386399</t>
+          <t>431887</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386399</t>
+          <t>431887</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>156709</t>
+          <t>152360</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>138570</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169833</t>
+          <t>167672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>145177</t>
+          <t>147563</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131321</t>
+          <t>134388</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156973</t>
+          <t>161184</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>301885</t>
+          <t>299923</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>281812</t>
+          <t>280374</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>320538</t>
+          <t>318758</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>66475</t>
+          <t>68231</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78866</t>
+          <t>80805</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>56786</t>
+          <t>58970</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69629</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>123260</t>
+          <t>127201</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140121</t>
+          <t>144439</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>31322</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40864</t>
+          <t>43995</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>46041</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>37122</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>55244</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>75799</t>
+          <t>80314</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>63972</t>
+          <t>69074</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>302610</t>
+          <t>349325</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>271795</t>
+          <t>318299</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>331595</t>
+          <t>380004</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>472530</t>
+          <t>330858</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>342633</t>
+          <t>305469</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>666318</t>
+          <t>356430</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>775141</t>
+          <t>680184</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>644961</t>
+          <t>638833</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1008050</t>
+          <t>721568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>236907</t>
+          <t>275903</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>208044</t>
+          <t>247400</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>268581</t>
+          <t>305298</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>281841</t>
+          <t>327797</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>136411</t>
+          <t>305161</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>379866</t>
+          <t>355314</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>518748</t>
+          <t>603700</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>339716</t>
+          <t>566711</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>618868</t>
+          <t>645213</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>76944</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>61142</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>95363</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>78637</t>
+          <t>94201</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>111487</t>
+          <t>112797</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>145621</t>
+          <t>171145</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>93194</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>180626</t>
+          <t>197908</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>25834</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>52706</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849104</t>
+          <t>771351</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849104</t>
+          <t>771351</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849104</t>
+          <t>771351</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1473383</t>
+          <t>1491039</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1473383</t>
+          <t>1491039</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1473383</t>
+          <t>1491039</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>552519</t>
+          <t>363015</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>402292</t>
+          <t>333162</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>766995</t>
+          <t>396323</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>317116</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>245967</t>
+          <t>290293</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>290679</t>
+          <t>344408</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>821231</t>
+          <t>680131</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>662534</t>
+          <t>638236</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1146081</t>
+          <t>717542</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>246344</t>
+          <t>287194</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>108769</t>
+          <t>257397</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>348149</t>
+          <t>315608</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>266082</t>
+          <t>307741</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>245169</t>
+          <t>282291</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>287714</t>
+          <t>332186</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>512425</t>
+          <t>594935</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>312228</t>
+          <t>558942</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>610709</t>
+          <t>636616</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>108571</t>
+          <t>123715</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>45343</t>
+          <t>104725</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>157719</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>163363</t>
+          <t>183847</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>145714</t>
+          <t>164356</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>183340</t>
+          <t>203739</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>271934</t>
+          <t>307562</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>159626</t>
+          <t>278115</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>331675</t>
+          <t>333785</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>927715</t>
+          <t>796950</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>927715</t>
+          <t>796950</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>927715</t>
+          <t>796950</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717136</t>
+          <t>830643</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717136</t>
+          <t>830643</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717136</t>
+          <t>830643</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644852</t>
+          <t>1627593</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644852</t>
+          <t>1627593</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644852</t>
+          <t>1627593</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1828811</t>
+          <t>1722901</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1679159</t>
+          <t>1650404</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2173471</t>
+          <t>1789014</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1613686</t>
+          <t>1576356</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1467580</t>
+          <t>1523413</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2037453</t>
+          <t>1639012</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>3442497</t>
+          <t>3299257</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3194979</t>
+          <t>3211076</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3926612</t>
+          <t>3385745</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1158759</t>
+          <t>1288878</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>907561</t>
+          <t>1231686</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1271478</t>
+          <t>1355857</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1429176</t>
+          <t>1473485</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1160249</t>
+          <t>1415883</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1560092</t>
+          <t>1525100</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2587934</t>
+          <t>2762363</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2268320</t>
+          <t>2680085</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2792173</t>
+          <t>2842346</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>384827</t>
+          <t>427608</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>303709</t>
+          <t>390934</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>430218</t>
+          <t>469130</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>532014</t>
+          <t>590228</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>429833</t>
+          <t>555382</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>585367</t>
+          <t>631569</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>916841</t>
+          <t>1017836</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>794288</t>
+          <t>969029</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>993940</t>
+          <t>1071633</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>73709</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>54502</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>96405</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>77060</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>93158</t>
+          <t>99560</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>178790</t>
+          <t>185781</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
